--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129976914</v>
+        <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>90946</v>
+        <v>92906</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>889</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,14 +1165,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685031</v>
+        <v>685174</v>
       </c>
       <c r="R6" t="n">
-        <v>6561690</v>
+        <v>6562053</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,13 +1231,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976914</t>
+          <t>https://artportalen.se/Sighting/136716247</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129976936</v>
+        <v>129976914</v>
       </c>
       <c r="B7" t="n">
         <v>90946</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685013</v>
+        <v>685031</v>
       </c>
       <c r="R7" t="n">
-        <v>6561705</v>
+        <v>6561690</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,13 +1337,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976936</t>
+          <t>https://artportalen.se/Sighting/129976914</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130155094</v>
+        <v>129976936</v>
       </c>
       <c r="B8" t="n">
         <v>90946</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685152</v>
+        <v>685013</v>
       </c>
       <c r="R8" t="n">
-        <v>6561703</v>
+        <v>6561705</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,19 +1411,19 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
@@ -1443,13 +1443,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155094</t>
+          <t>https://artportalen.se/Sighting/129976936</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130306117</v>
+        <v>130155094</v>
       </c>
       <c r="B9" t="n">
         <v>90946</v>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685116</v>
+        <v>685152</v>
       </c>
       <c r="R9" t="n">
-        <v>6561716</v>
+        <v>6561703</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,16 +1549,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130306117</t>
+          <t>https://artportalen.se/Sighting/130155094</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130121568</v>
+        <v>130306117</v>
       </c>
       <c r="B10" t="n">
-        <v>92134</v>
+        <v>90946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,21 +1566,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1106</v>
+        <v>889</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,17 +1589,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685143</v>
+        <v>685116</v>
       </c>
       <c r="R10" t="n">
-        <v>6561740</v>
+        <v>6561716</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,17 +1623,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Kanske 3 fruktkroppar på granlåga</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,45 +1641,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121568</t>
+          <t>https://artportalen.se/Sighting/130306117</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130009151</v>
+        <v>130121568</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>92134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,21 +1672,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1715,17 +1695,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685139</v>
+        <v>685143</v>
       </c>
       <c r="R11" t="n">
-        <v>6562022</v>
+        <v>6561740</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,70 +1729,90 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kanske 3 fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009151</t>
+          <t>https://artportalen.se/Sighting/130121568</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130009195</v>
+        <v>130009151</v>
       </c>
       <c r="B12" t="n">
-        <v>92564</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685160</v>
+        <v>685139</v>
       </c>
       <c r="R12" t="n">
-        <v>6561999</v>
+        <v>6562022</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,11 +1863,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gran, på halvhög stubbe samt på lågan.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1892,16 +1887,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009195</t>
+          <t>https://artportalen.se/Sighting/130009151</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96806135</v>
+        <v>130009195</v>
       </c>
       <c r="B13" t="n">
-        <v>92348</v>
+        <v>92564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,21 +1904,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>684987</v>
+        <v>685160</v>
       </c>
       <c r="R13" t="n">
-        <v>6561670</v>
+        <v>6561999</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,12 +1961,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran, på halvhög stubbe samt på lågan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,13 +1998,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96806135</t>
+          <t>https://artportalen.se/Sighting/130009195</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130155389</v>
+        <v>96806135</v>
       </c>
       <c r="B14" t="n">
         <v>92348</v>
@@ -2045,10 +2045,10 @@
         <v>684987</v>
       </c>
       <c r="R14" t="n">
-        <v>6561666</v>
+        <v>6561670</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,17 +2072,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tidigare rapporterad 2021.</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,38 +2104,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155389</t>
+          <t>https://artportalen.se/Sighting/96806135</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99759702</v>
+        <v>130155389</v>
       </c>
       <c r="B15" t="n">
-        <v>91930</v>
+        <v>92348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685013</v>
+        <v>684987</v>
       </c>
       <c r="R15" t="n">
-        <v>6561713</v>
+        <v>6561666</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,12 +2178,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,13 +2215,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99759702</t>
+          <t>https://artportalen.se/Sighting/130155389</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129976928</v>
+        <v>99759702</v>
       </c>
       <c r="B16" t="n">
         <v>91930</v>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685018</v>
+        <v>685013</v>
       </c>
       <c r="R16" t="n">
         <v>6561713</v>
@@ -2289,17 +2289,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Återfynd, tidigare rapporterad 2022. Tallen börjar se lite tärd ut.</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2326,13 +2321,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976928</t>
+          <t>https://artportalen.se/Sighting/99759702</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129976940</v>
+        <v>129976928</v>
       </c>
       <c r="B17" t="n">
         <v>91930</v>
@@ -2370,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685014</v>
+        <v>685018</v>
       </c>
       <c r="R17" t="n">
-        <v>6561677</v>
+        <v>6561713</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2410,7 +2405,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Två gamla tickor på död tall.</t>
+          <t>Återfynd, tidigare rapporterad 2022. Tallen börjar se lite tärd ut.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,13 +2432,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976940</t>
+          <t>https://artportalen.se/Sighting/129976928</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130125932</v>
+        <v>129976940</v>
       </c>
       <c r="B18" t="n">
         <v>91930</v>
@@ -2471,24 +2466,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tyresta by, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685171</v>
+        <v>685014</v>
       </c>
       <c r="R18" t="n">
-        <v>6561736</v>
+        <v>6561677</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2515,12 +2506,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två gamla tickor på död tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,24 +2532,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130125932</t>
+          <t>https://artportalen.se/Sighting/129976940</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130155377</v>
+        <v>130125932</v>
       </c>
       <c r="B19" t="n">
         <v>91930</v>
@@ -2581,20 +2577,24 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685086</v>
+        <v>685171</v>
       </c>
       <c r="R19" t="n">
-        <v>6561624</v>
+        <v>6561736</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2621,17 +2621,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På en gren, tallen intill betesmark.</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2647,63 +2642,54 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155377</t>
+          <t>https://artportalen.se/Sighting/130125932</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130009940</v>
+        <v>130155377</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>91930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2711,10 +2697,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685147</v>
+        <v>685086</v>
       </c>
       <c r="R20" t="n">
-        <v>6561847</v>
+        <v>6561624</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2741,17 +2727,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Bearbetad tallraka.</t>
+          <t>På en gren, tallen intill betesmark.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,6 +2746,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2777,52 +2764,43 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009940</t>
+          <t>https://artportalen.se/Sighting/130155377</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130328335</v>
+        <v>136716534</v>
       </c>
       <c r="B21" t="n">
-        <v>57950</v>
+        <v>91590</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5741</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2830,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685025</v>
+        <v>685106</v>
       </c>
       <c r="R21" t="n">
-        <v>6561653</v>
+        <v>6561846</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,17 +2838,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bearbetad gammal björk, fullt av flisor på en knärotslokal.</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2879,6 +2852,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2896,49 +2870,43 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130328335</t>
+          <t>https://artportalen.se/Sighting/136716534</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111153798</v>
+        <v>136716493</v>
       </c>
       <c r="B22" t="n">
-        <v>56895</v>
+        <v>93440</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100088</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2946,13 +2914,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685167</v>
+        <v>685170</v>
       </c>
       <c r="R22" t="n">
-        <v>6561941</v>
+        <v>6562056</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2976,12 +2944,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,16 +2976,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111153798</t>
+          <t>https://artportalen.se/Sighting/136716493</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130121570</v>
+        <v>136716557</v>
       </c>
       <c r="B23" t="n">
-        <v>44177</v>
+        <v>92784</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,46 +2993,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101735</v>
+        <v>6031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685100</v>
+        <v>684997</v>
       </c>
       <c r="R23" t="n">
-        <v>6561680</v>
+        <v>6561647</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3088,17 +3050,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gräs gick in typ 10 cm</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,57 +3071,61 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121570</t>
+          <t>https://artportalen.se/Sighting/136716557</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129976909</v>
+        <v>130009940</v>
       </c>
       <c r="B24" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3174,13 +3135,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685130</v>
+        <v>685147</v>
       </c>
       <c r="R24" t="n">
-        <v>6561726</v>
+        <v>6561847</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3204,12 +3165,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bearbetad tallraka.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,44 +3201,52 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976909</t>
+          <t>https://artportalen.se/Sighting/130009940</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130328836</v>
+        <v>130328335</v>
       </c>
       <c r="B25" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3280,10 +3254,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685072</v>
+        <v>685025</v>
       </c>
       <c r="R25" t="n">
-        <v>6561690</v>
+        <v>6561653</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,12 +3284,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bearbetad gammal björk, fullt av flisor på en knärotslokal.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3341,16 +3320,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130328836</t>
+          <t>https://artportalen.se/Sighting/130328335</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130121567</v>
+        <v>111153798</v>
       </c>
       <c r="B26" t="n">
-        <v>5199</v>
+        <v>56895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,16 +3337,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>100088</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3375,29 +3354,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685133</v>
+        <v>685167</v>
       </c>
       <c r="R26" t="n">
-        <v>6561742</v>
+        <v>6561941</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3421,12 +3400,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,27 +3421,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121567</t>
+          <t>https://artportalen.se/Sighting/111153798</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130155159</v>
+        <v>130121570</v>
       </c>
       <c r="B27" t="n">
-        <v>8455</v>
+        <v>44177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,21 +3449,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3499,17 +3478,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685023</v>
+        <v>685100</v>
       </c>
       <c r="R27" t="n">
-        <v>6561678</v>
+        <v>6561680</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3533,12 +3512,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gräs gick in typ 10 cm</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3554,74 +3538,73 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155159</t>
+          <t>https://artportalen.se/Sighting/130121570</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130121571</v>
+        <v>129976909</v>
       </c>
       <c r="B28" t="n">
-        <v>8444</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685103</v>
+        <v>685130</v>
       </c>
       <c r="R28" t="n">
-        <v>6561668</v>
+        <v>6561726</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3645,12 +3628,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3659,62 +3642,61 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121571</t>
+          <t>https://artportalen.se/Sighting/129976909</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130155175</v>
+        <v>130328836</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3722,10 +3704,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685025</v>
+        <v>685072</v>
       </c>
       <c r="R29" t="n">
-        <v>6561654</v>
+        <v>6561690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3752,17 +3734,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3771,7 +3748,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3788,6 +3764,454 @@
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130328836</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130121567</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>A 59567-2025, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>685133</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6561742</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121567</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130155159</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>685023</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6561678</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155159</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130121571</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 59567-2025, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>685103</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6561668</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121571</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130155175</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>685025</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6561654</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130155175</t>
         </is>
@@ -3823,6 +4247,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136716534</v>
       </c>
       <c r="B21" t="n">
-        <v>91590</v>
+        <v>91592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136716493</v>
       </c>
       <c r="B22" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136716557</v>
       </c>
       <c r="B23" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92911</v>
+        <v>92913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136716534</v>
       </c>
       <c r="B21" t="n">
-        <v>91592</v>
+        <v>91594</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>136716493</v>
       </c>
       <c r="B22" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>136716557</v>
       </c>
       <c r="B23" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129976914</v>
+        <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>90946</v>
+        <v>92913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>889</v>
+        <v>366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,14 +1271,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685031</v>
+        <v>685221</v>
       </c>
       <c r="R7" t="n">
-        <v>6561690</v>
+        <v>6561731</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,12 +1305,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Återfynd. Tidigare rapporterad 2025.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,13 +1342,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976914</t>
+          <t>https://artportalen.se/Sighting/136991960</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129976936</v>
+        <v>129976914</v>
       </c>
       <c r="B8" t="n">
         <v>90946</v>
@@ -1381,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685013</v>
+        <v>685031</v>
       </c>
       <c r="R8" t="n">
-        <v>6561705</v>
+        <v>6561690</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,13 +1448,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976936</t>
+          <t>https://artportalen.se/Sighting/129976914</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130155094</v>
+        <v>129976936</v>
       </c>
       <c r="B9" t="n">
         <v>90946</v>
@@ -1487,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685152</v>
+        <v>685013</v>
       </c>
       <c r="R9" t="n">
-        <v>6561703</v>
+        <v>6561705</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,19 +1522,19 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
@@ -1549,13 +1554,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155094</t>
+          <t>https://artportalen.se/Sighting/129976936</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130306117</v>
+        <v>130155094</v>
       </c>
       <c r="B10" t="n">
         <v>90946</v>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685116</v>
+        <v>685152</v>
       </c>
       <c r="R10" t="n">
-        <v>6561716</v>
+        <v>6561703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,16 +1660,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130306117</t>
+          <t>https://artportalen.se/Sighting/130155094</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130121568</v>
+        <v>130306117</v>
       </c>
       <c r="B11" t="n">
-        <v>92134</v>
+        <v>90946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,21 +1677,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1106</v>
+        <v>889</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,17 +1700,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685143</v>
+        <v>685116</v>
       </c>
       <c r="R11" t="n">
-        <v>6561740</v>
+        <v>6561716</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,17 +1734,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kanske 3 fruktkroppar på granlåga</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,45 +1752,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121568</t>
+          <t>https://artportalen.se/Sighting/130306117</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130009151</v>
+        <v>130121568</v>
       </c>
       <c r="B12" t="n">
-        <v>91909</v>
+        <v>92134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,21 +1783,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1821,17 +1806,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685139</v>
+        <v>685143</v>
       </c>
       <c r="R12" t="n">
-        <v>6562022</v>
+        <v>6561740</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,70 +1840,90 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kanske 3 fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009151</t>
+          <t>https://artportalen.se/Sighting/130121568</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130009195</v>
+        <v>130009151</v>
       </c>
       <c r="B13" t="n">
-        <v>92564</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685160</v>
+        <v>685139</v>
       </c>
       <c r="R13" t="n">
-        <v>6561999</v>
+        <v>6562022</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,11 +1974,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran, på halvhög stubbe samt på lågan.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1998,16 +1998,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009195</t>
+          <t>https://artportalen.se/Sighting/130009151</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96806135</v>
+        <v>130009195</v>
       </c>
       <c r="B14" t="n">
-        <v>92348</v>
+        <v>92564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,21 +2015,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2042,13 +2042,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>684987</v>
+        <v>685160</v>
       </c>
       <c r="R14" t="n">
-        <v>6561670</v>
+        <v>6561999</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,12 +2072,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran, på halvhög stubbe samt på lågan.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,13 +2109,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96806135</t>
+          <t>https://artportalen.se/Sighting/130009195</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130155389</v>
+        <v>96806135</v>
       </c>
       <c r="B15" t="n">
         <v>92348</v>
@@ -2151,10 +2156,10 @@
         <v>684987</v>
       </c>
       <c r="R15" t="n">
-        <v>6561666</v>
+        <v>6561670</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2178,17 +2183,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Tidigare rapporterad 2021.</t>
+          <t>2021-10-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,38 +2215,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155389</t>
+          <t>https://artportalen.se/Sighting/96806135</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>99759702</v>
+        <v>130155389</v>
       </c>
       <c r="B16" t="n">
-        <v>91930</v>
+        <v>92348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685013</v>
+        <v>684987</v>
       </c>
       <c r="R16" t="n">
-        <v>6561713</v>
+        <v>6561666</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,12 +2289,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2321,13 +2326,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99759702</t>
+          <t>https://artportalen.se/Sighting/130155389</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129976928</v>
+        <v>99759702</v>
       </c>
       <c r="B17" t="n">
         <v>91930</v>
@@ -2365,7 +2370,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685018</v>
+        <v>685013</v>
       </c>
       <c r="R17" t="n">
         <v>6561713</v>
@@ -2395,17 +2400,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Återfynd, tidigare rapporterad 2022. Tallen börjar se lite tärd ut.</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2432,13 +2432,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976928</t>
+          <t>https://artportalen.se/Sighting/99759702</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129976940</v>
+        <v>129976928</v>
       </c>
       <c r="B18" t="n">
         <v>91930</v>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685014</v>
+        <v>685018</v>
       </c>
       <c r="R18" t="n">
-        <v>6561677</v>
+        <v>6561713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Två gamla tickor på död tall.</t>
+          <t>Återfynd, tidigare rapporterad 2022. Tallen börjar se lite tärd ut.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2543,13 +2543,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976940</t>
+          <t>https://artportalen.se/Sighting/129976928</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130125932</v>
+        <v>129976940</v>
       </c>
       <c r="B19" t="n">
         <v>91930</v>
@@ -2577,24 +2577,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tyresta by, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685171</v>
+        <v>685014</v>
       </c>
       <c r="R19" t="n">
-        <v>6561736</v>
+        <v>6561677</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2621,12 +2617,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Två gamla tickor på död tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2642,24 +2643,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130125932</t>
+          <t>https://artportalen.se/Sighting/129976940</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130155377</v>
+        <v>130125932</v>
       </c>
       <c r="B20" t="n">
         <v>91930</v>
@@ -2687,20 +2688,24 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685086</v>
+        <v>685171</v>
       </c>
       <c r="R20" t="n">
-        <v>6561624</v>
+        <v>6561736</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,17 +2732,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en gren, tallen intill betesmark.</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,27 +2753,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155377</t>
+          <t>https://artportalen.se/Sighting/130125932</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136716534</v>
+        <v>130155377</v>
       </c>
       <c r="B21" t="n">
-        <v>91594</v>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,21 +2781,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5741</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685106</v>
+        <v>685086</v>
       </c>
       <c r="R21" t="n">
-        <v>6561846</v>
+        <v>6561624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2838,12 +2838,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På en gren, tallen intill betesmark.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2870,16 +2875,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136716534</t>
+          <t>https://artportalen.se/Sighting/130155377</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136716493</v>
+        <v>136716534</v>
       </c>
       <c r="B22" t="n">
-        <v>93447</v>
+        <v>91594</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2887,21 +2892,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2910,17 +2915,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685170</v>
+        <v>685106</v>
       </c>
       <c r="R22" t="n">
-        <v>6562056</v>
+        <v>6561846</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2976,38 +2981,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136716493</t>
+          <t>https://artportalen.se/Sighting/136716534</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136716557</v>
+        <v>136716493</v>
       </c>
       <c r="B23" t="n">
-        <v>92791</v>
+        <v>93447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6031</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3016,17 +3021,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684997</v>
+        <v>685170</v>
       </c>
       <c r="R23" t="n">
-        <v>6561647</v>
+        <v>6562056</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3082,16 +3087,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136716557</t>
+          <t>https://artportalen.se/Sighting/136716493</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130009940</v>
+        <v>136716557</v>
       </c>
       <c r="B24" t="n">
-        <v>57950</v>
+        <v>92791</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3099,35 +3104,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3135,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685147</v>
+        <v>684997</v>
       </c>
       <c r="R24" t="n">
-        <v>6561847</v>
+        <v>6561647</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3165,17 +3161,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bearbetad tallraka.</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3184,6 +3175,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3201,13 +3193,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009940</t>
+          <t>https://artportalen.se/Sighting/136716557</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130328335</v>
+        <v>130009940</v>
       </c>
       <c r="B25" t="n">
         <v>57950</v>
@@ -3254,10 +3246,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685025</v>
+        <v>685147</v>
       </c>
       <c r="R25" t="n">
-        <v>6561653</v>
+        <v>6561847</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3284,17 +3276,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Bearbetad gammal björk, fullt av flisor på en knärotslokal.</t>
+          <t>Bearbetad tallraka.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3320,16 +3312,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130328335</t>
+          <t>https://artportalen.se/Sighting/130009940</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111153798</v>
+        <v>130328335</v>
       </c>
       <c r="B26" t="n">
-        <v>56895</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,16 +3329,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3359,21 +3351,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685167</v>
+        <v>685025</v>
       </c>
       <c r="R26" t="n">
-        <v>6561941</v>
+        <v>6561653</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3400,12 +3395,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bearbetad gammal björk, fullt av flisor på en knärotslokal.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,7 +3414,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3432,16 +3431,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111153798</t>
+          <t>https://artportalen.se/Sighting/130328335</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130121570</v>
+        <v>111153798</v>
       </c>
       <c r="B27" t="n">
-        <v>44177</v>
+        <v>56895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,46 +3448,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>100088</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685100</v>
+        <v>685167</v>
       </c>
       <c r="R27" t="n">
-        <v>6561680</v>
+        <v>6561941</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3512,17 +3511,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gräs gick in typ 10 cm</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3538,73 +3532,74 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121570</t>
+          <t>https://artportalen.se/Sighting/111153798</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129976909</v>
+        <v>130121570</v>
       </c>
       <c r="B28" t="n">
-        <v>58114</v>
+        <v>44177</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685130</v>
+        <v>685100</v>
       </c>
       <c r="R28" t="n">
-        <v>6561726</v>
+        <v>6561680</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3628,12 +3623,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gräs gick in typ 10 cm</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3642,30 +3642,31 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129976909</t>
+          <t>https://artportalen.se/Sighting/130121570</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130328836</v>
+        <v>129976909</v>
       </c>
       <c r="B29" t="n">
         <v>58114</v>
@@ -3696,7 +3697,11 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3704,13 +3709,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685072</v>
+        <v>685130</v>
       </c>
       <c r="R29" t="n">
-        <v>6561690</v>
+        <v>6561726</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3734,12 +3739,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3765,63 +3770,58 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130328836</t>
+          <t>https://artportalen.se/Sighting/129976909</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130121567</v>
+        <v>130328836</v>
       </c>
       <c r="B30" t="n">
-        <v>5199</v>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685133</v>
+        <v>685072</v>
       </c>
       <c r="R30" t="n">
-        <v>6561742</v>
+        <v>6561690</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3845,12 +3845,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3859,34 +3859,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121567</t>
+          <t>https://artportalen.se/Sighting/130328836</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130155159</v>
+        <v>130121567</v>
       </c>
       <c r="B31" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,21 +3893,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3923,17 +3922,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685023</v>
+        <v>685133</v>
       </c>
       <c r="R31" t="n">
-        <v>6561678</v>
+        <v>6561742</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3957,12 +3956,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3978,27 +3977,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155159</t>
+          <t>https://artportalen.se/Sighting/130121567</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130121571</v>
+        <v>130155159</v>
       </c>
       <c r="B32" t="n">
-        <v>8444</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4006,21 +4005,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4035,17 +4034,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 59567-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685103</v>
+        <v>685023</v>
       </c>
       <c r="R32" t="n">
-        <v>6561668</v>
+        <v>6561678</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4069,12 +4068,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4090,69 +4089,74 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121571</t>
+          <t>https://artportalen.se/Sighting/130155159</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130155175</v>
+        <v>130121571</v>
       </c>
       <c r="B33" t="n">
-        <v>99118</v>
+        <v>8444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59567-2025, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685025</v>
+        <v>685103</v>
       </c>
       <c r="R33" t="n">
-        <v>6561654</v>
+        <v>6561668</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4176,17 +4180,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4202,16 +4201,128 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121571</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130155175</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>685025</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6561654</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis ca 50 ex varav tre med fröställningar.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130155175</t>
         </is>
@@ -4251,6 +4362,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136716534</v>
       </c>
       <c r="B22" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>136716493</v>
       </c>
       <c r="B23" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136716557</v>
       </c>
       <c r="B24" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136716534</v>
       </c>
       <c r="B22" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>136716493</v>
       </c>
       <c r="B23" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136716557</v>
       </c>
       <c r="B24" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136716534</v>
       </c>
       <c r="B22" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>136716493</v>
       </c>
       <c r="B23" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136716557</v>
       </c>
       <c r="B24" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136716534</v>
       </c>
       <c r="B22" t="n">
-        <v>91599</v>
+        <v>91605</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>136716493</v>
       </c>
       <c r="B23" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136716557</v>
       </c>
       <c r="B24" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136716534</v>
       </c>
       <c r="B22" t="n">
-        <v>91605</v>
+        <v>91609</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>136716493</v>
       </c>
       <c r="B23" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136716557</v>
       </c>
       <c r="B24" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136716534</v>
       </c>
       <c r="B22" t="n">
-        <v>91609</v>
+        <v>91611</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>136716493</v>
       </c>
       <c r="B23" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136716557</v>
       </c>
       <c r="B24" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136716534</v>
       </c>
       <c r="B22" t="n">
-        <v>91611</v>
+        <v>91624</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>136716493</v>
       </c>
       <c r="B23" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136716557</v>
       </c>
       <c r="B24" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136716534</v>
       </c>
       <c r="B22" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>136716493</v>
       </c>
       <c r="B23" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136716557</v>
       </c>
       <c r="B24" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136716534</v>
       </c>
       <c r="B22" t="n">
-        <v>91626</v>
+        <v>91629</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>136716493</v>
       </c>
       <c r="B23" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136716557</v>
       </c>
       <c r="B24" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,7 +1134,7 @@
         <v>136716247</v>
       </c>
       <c r="B6" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136716534</v>
       </c>
       <c r="B22" t="n">
-        <v>91629</v>
+        <v>91639</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>136716493</v>
       </c>
       <c r="B23" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>136716557</v>
       </c>
       <c r="B24" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4325,6 +4325,113 @@
       <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130155175</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136716181</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93469</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>685163</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6562051</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Röd saft.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136716181</t>
         </is>
       </c>
     </row>
@@ -4363,6 +4470,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>136716181</v>
       </c>
       <c r="B35" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>136716181</v>
       </c>
       <c r="B35" t="n">
-        <v>93470</v>
+        <v>93475</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>136716181</v>
       </c>
       <c r="B35" t="n">
-        <v>93475</v>
+        <v>93477</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>136716181</v>
       </c>
       <c r="B35" t="n">
-        <v>93477</v>
+        <v>93483</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>136716181</v>
       </c>
       <c r="B35" t="n">
-        <v>93483</v>
+        <v>93495</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>136716181</v>
       </c>
       <c r="B35" t="n">
-        <v>93495</v>
+        <v>93496</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>136716181</v>
       </c>
       <c r="B35" t="n">
-        <v>93496</v>
+        <v>93499</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92985</v>
+        <v>92986</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 59567-2025 artfynd.xlsx
+++ b/artfynd/A 59567-2025 artfynd.xlsx
@@ -1240,7 +1240,7 @@
         <v>136991960</v>
       </c>
       <c r="B7" t="n">
-        <v>92986</v>
+        <v>92989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>136716181</v>
       </c>
       <c r="B35" t="n">
-        <v>93499</v>
+        <v>93503</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
